--- a/test-data/xlsx/import_preview_mixed.xlsx
+++ b/test-data/xlsx/import_preview_mixed.xlsx
@@ -20,124 +20,51 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
-  <si>
-    <t xml:space="preserve">jobTitle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">companyName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">workType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">salaryRange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateApplied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">statusDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">source</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+  <si>
+    <t xml:space="preserve">Job Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employment Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date Applied</t>
   </si>
   <si>
     <t xml:space="preserve">Software Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">AlphaTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New York, NY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remote</t>
+    <t xml:space="preserve">Google</t>
   </si>
   <si>
     <t xml:space="preserve">Full-time</t>
   </si>
   <si>
-    <t xml:space="preserve">$80,000 - $120,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APPLIED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://example.com/jobs/1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LinkedIn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissingTitleCorp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chicago, IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$90,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://example.com/jobs/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indeed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austin, TX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hybrid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$95,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://example.com/jobs/3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glassdoor</t>
+    <t xml:space="preserve">Amazon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contract</t>
   </si>
   <si>
     <t xml:space="preserve">Data Analyst</t>
   </si>
   <si>
-    <t xml:space="preserve">DataWorks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$65,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://example.com/jobs/4</t>
+    <t xml:space="preserve">Product Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="@"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -203,16 +130,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -339,20 +262,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="23.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11.75"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -368,139 +284,55 @@
       <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>46027</v>
-      </c>
-      <c r="H2" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="0" t="s">
-        <v>19</v>
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>46032</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="0" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>46028</v>
-      </c>
-      <c r="J3" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="0" t="s">
-        <v>24</v>
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>46034</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>46029</v>
-      </c>
-      <c r="J4" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="0" t="s">
-        <v>30</v>
+        <v>6</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>46037</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>46030</v>
-      </c>
-      <c r="J5" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" s="0" t="s">
-        <v>19</v>
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46042</v>
       </c>
     </row>
   </sheetData>
